--- a/table_from_link/37002253_table3.xlsx
+++ b/table_from_link/37002253_table3.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Genera</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Samples</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>R 2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Coeff</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>SNP#</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SampleSize</t>
         </is>
@@ -486,11 +474,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0.3705</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.0068</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.3705</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.0068</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -499,17 +491,23 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>− 1870.66</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>524</v>
-      </c>
-      <c r="H2" t="n">
-        <v>101798</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2571</v>
+          <t>− 1870.66</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>524.00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>101798</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -523,11 +521,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0036</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.0020</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.0036</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -536,17 +538,23 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>− 224.26</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>108.71</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1684</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1577</v>
+          <t>− 224.26</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>108.71</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1684</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -560,11 +568,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>0.1676</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.008</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.1676</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.0080</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -576,14 +588,20 @@
           <t>2581.83</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>665.28</v>
-      </c>
-      <c r="H4" t="n">
-        <v>67574</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2571</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>665.28</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>67574</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -597,11 +615,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0.3246</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.0023</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.3246</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.0023</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -610,17 +632,23 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>− 2953.44</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1810.61</v>
-      </c>
-      <c r="H5" t="n">
-        <v>99785</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1577</v>
+          <t>− 2953.44</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1810.61</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>99785</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -634,11 +662,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.0078</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0032</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.0078</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -647,17 +679,23 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>− 469.15</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>121.86</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2834</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2571</v>
+          <t>− 469.15</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>121.86</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -671,11 +709,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>0.2989</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.0054</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.2989</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.0054</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -687,14 +729,20 @@
           <t>4134.46</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>1641.01</v>
-      </c>
-      <c r="H7" t="n">
-        <v>96076</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1577</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1641.01</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>96076</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -708,11 +756,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>0.1792</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0114</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.1792</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.0114</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -724,14 +776,20 @@
           <t>3930.96</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>845.35</v>
-      </c>
-      <c r="H8" t="n">
-        <v>71984</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2571</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>845.35</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>71984</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -745,11 +803,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.0037</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.0037</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -761,14 +823,20 @@
           <t>221.55</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>106.1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>922</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1577</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>106.10</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -782,11 +850,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.008999999999999999</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.0002</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.0090</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -795,17 +867,23 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>− 71.29</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="H10" t="n">
-        <v>177</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2571</v>
+          <t>− 71.29</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>17.22</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -819,11 +897,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>0.0199</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.002</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.0199</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.0020</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -832,17 +914,23 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>− 404.97</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>265.96</v>
-      </c>
-      <c r="H11" t="n">
-        <v>12431</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1577</v>
+          <t>− 404.97</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>265.96</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>12431</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -856,11 +944,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>0.3839</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.008200000000000001</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.3839</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.0082</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -869,17 +961,23 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>− 1276.68</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>324.95</v>
-      </c>
-      <c r="H12" t="n">
-        <v>71434</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2571</v>
+          <t>− 1276.68</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>324.95</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>71434</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -893,11 +991,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>0.08309999999999999</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.008</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.0831</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.0080</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -909,14 +1011,20 @@
           <t>1068.34</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>347.56</v>
-      </c>
-      <c r="H13" t="n">
-        <v>25728</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1577</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>347.56</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>25728</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -930,11 +1038,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0073</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.0002</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.0073</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -946,14 +1058,20 @@
           <t>125.63</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>33.51</v>
-      </c>
-      <c r="H14" t="n">
-        <v>230</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2571</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>33.51</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -967,11 +1085,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>0.0003</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.0143</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.0003</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.0143</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -983,14 +1105,20 @@
           <t>229.15</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>56.06</v>
-      </c>
-      <c r="H15" t="n">
-        <v>335</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1577</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>56.06</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1004,11 +1132,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>0.1049</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.008200000000000001</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.1049</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.0082</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1017,17 +1149,23 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>− 858.39</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>220.13</v>
-      </c>
-      <c r="H16" t="n">
-        <v>42727</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2571</v>
+          <t>− 858.39</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>220.13</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>42727</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1041,11 +1179,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>0.0439</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.0066</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.0439</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.0066</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1054,17 +1196,23 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>− 1131.73</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>405.7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>22002</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1577</v>
+          <t>− 1131.73</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>405.70</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>22002</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1078,11 +1226,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.0086</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.1020</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.0086</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1091,17 +1243,23 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>− 1085.22</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>273.37</v>
-      </c>
-      <c r="H18" t="n">
-        <v>48130</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2571</v>
+          <t>− 1085.22</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>273.37</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>48130</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1115,11 +1273,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>0.0101</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.0038</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.0101</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.0038</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1131,14 +1293,20 @@
           <t>707.65</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>333.01</v>
-      </c>
-      <c r="H19" t="n">
-        <v>7483</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1577</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>333.01</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>7483</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1152,11 +1320,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>0.0404</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.007</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.0404</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.0070</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1165,17 +1337,23 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>− 418.31</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>115.71</v>
-      </c>
-      <c r="H20" t="n">
-        <v>19567</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2571</v>
+          <t>− 418.31</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>115.71</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>19567</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1189,11 +1367,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.008999999999999999</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.0008</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.0090</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1202,17 +1384,23 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>− 142.85</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>44.01</v>
-      </c>
-      <c r="H21" t="n">
-        <v>663</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1577</v>
+          <t>− 142.85</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>44.01</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1226,11 +1414,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>0.4353</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.0072</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.4353</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.0072</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1239,17 +1431,23 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>− 1240.65</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>338.95</v>
-      </c>
-      <c r="H22" t="n">
-        <v>95579</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2571</v>
+          <t>− 1240.65</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>338.95</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>95579</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1263,11 +1461,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>0.1259</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.0025</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.1259</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.0025</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1276,17 +1478,23 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>− 805.51</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>472.45</v>
-      </c>
-      <c r="H23" t="n">
-        <v>42817</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1577</v>
+          <t>− 805.51</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>472.45</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>42817</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1300,11 +1508,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0089</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.0330</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.0089</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1313,17 +1525,23 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>− 254.45</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>63.13</v>
-      </c>
-      <c r="H24" t="n">
-        <v>16821</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2571</v>
+          <t>− 254.45</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>63.13</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>16821</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1337,11 +1555,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>0.0116</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0039</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.0116</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.0039</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1350,17 +1572,23 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>− 351.65</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>164.98</v>
-      </c>
-      <c r="H25" t="n">
-        <v>7135</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1577</v>
+          <t>− 351.65</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>164.98</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>7135</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1374,11 +1602,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>0.1903</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0154</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.1903</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0.0154</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1387,17 +1619,23 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>− 3014.37</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>566.17</v>
-      </c>
-      <c r="H26" t="n">
-        <v>70292</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2571</v>
+          <t>− 3014.37</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>566.17</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>70292</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1411,11 +1649,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.0024</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.0024</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.0024</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1424,17 +1666,23 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>− 246.05</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>146.1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2152</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1577</v>
+          <t>− 246.05</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>146.10</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2152</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1448,11 +1696,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>0.0034</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.0067</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.0034</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.0067</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1464,14 +1716,20 @@
           <t>530.79</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>147.83</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2997</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2571</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>147.83</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2997</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1485,11 +1743,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.0021</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.0004</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1501,14 +1763,20 @@
           <t>113.71</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>71.44</v>
-      </c>
-      <c r="H29" t="n">
-        <v>439</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1577</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>71.44</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1522,11 +1790,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.0784</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0081</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.0784</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.0081</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1535,17 +1807,23 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>− 776.50</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>200.53</v>
-      </c>
-      <c r="H30" t="n">
-        <v>35344</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2571</v>
+          <t>− 776.50</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>200.53</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>35344</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1559,11 +1837,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>0.0041</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.0017</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.0041</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.0017</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1575,14 +1857,20 @@
           <t>197.29</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>139.4</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3224</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1577</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>139.40</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1596,11 +1884,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>0.0124</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.0068</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.0124</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.0068</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1609,17 +1901,23 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>− 630.36</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>174.67</v>
-      </c>
-      <c r="H32" t="n">
-        <v>8305</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2571</v>
+          <t>− 630.36</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>174.67</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>8305</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1633,11 +1931,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.0027</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0.0051</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1649,14 +1951,20 @@
           <t>302.62</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>170.24</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3884</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1577</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>170.24</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3884</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1670,11 +1978,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>0.008399999999999999</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.0075</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0.0084</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.0075</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1683,17 +1995,23 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>− 556.34</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>147.21</v>
-      </c>
-      <c r="H34" t="n">
-        <v>6609</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2571</v>
+          <t>− 556.34</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>147.21</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6609</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1707,11 +2025,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.0031</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0.0008</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.0031</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1720,17 +2042,23 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>− 147.32</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>76.68000000000001</v>
-      </c>
-      <c r="H35" t="n">
-        <v>819</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1577</v>
+          <t>− 147.32</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>76.68</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1744,11 +2072,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>0.2061</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.01</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0.2061</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.0100</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1757,17 +2089,23 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>− 3564.78</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>819.1799999999999</v>
-      </c>
-      <c r="H36" t="n">
-        <v>78446</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2571</v>
+          <t>− 3564.78</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>819.18</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>78446</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1781,11 +2119,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.0027</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0.0037</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.0027</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1794,17 +2136,23 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>− 366.88</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>207.02</v>
-      </c>
-      <c r="H37" t="n">
-        <v>3135</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1577</v>
+          <t>− 366.88</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>207.02</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3135</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1818,11 +2166,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>0.4928</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.0071</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0.4928</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.0071</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1834,14 +2186,20 @@
           <t>3594.16</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>982.2</v>
-      </c>
-      <c r="H38" t="n">
-        <v>124985</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2571</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>982.20</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>124985</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1855,11 +2213,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.0009</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0.0002</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.0009</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1868,17 +2230,23 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>− 34.75</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="H39" t="n">
-        <v>156</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1577</v>
+          <t>− 34.75</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>34.10</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1892,11 +2260,15 @@
           <t>ADc12</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.0081</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0.0070</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.0081</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1908,14 +2280,20 @@
           <t>539.94</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>137.72</v>
-      </c>
-      <c r="H40" t="n">
-        <v>5406</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2571</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>137.72</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5406</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1929,11 +2307,15 @@
           <t>GenADA</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.008500000000000001</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.0021</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.0085</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1945,14 +2327,20 @@
           <t>369.43</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>116.78</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1843</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1577</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>116.78</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
       </c>
     </row>
   </sheetData>
